--- a/partial/sliding_window_results_window_8.xlsx
+++ b/partial/sliding_window_results_window_8.xlsx
@@ -463,13 +463,13 @@
         <v>29.84</v>
       </c>
       <c r="C2" t="n">
-        <v>30.46084261169721</v>
+        <v>30.26572128279039</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6208426116972099</v>
+        <v>0.4257212827903949</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3854455484990125</v>
+        <v>0.1812386106206994</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.81</v>
       </c>
       <c r="C3" t="n">
-        <v>30.3136293851742</v>
+        <v>30.13497992549404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5036293851742037</v>
+        <v>0.3249799254940449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2536425576109465</v>
+        <v>0.105611951974115</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.92</v>
       </c>
       <c r="C4" t="n">
-        <v>30.13339726642423</v>
+        <v>29.88282032601017</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2133972664242272</v>
+        <v>-0.03717967398983291</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0455383933173326</v>
+        <v>0.001382328157990258</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.98</v>
       </c>
       <c r="C5" t="n">
-        <v>29.5414924624566</v>
+        <v>29.89411918165291</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4385075375434049</v>
+        <v>-0.08588081834708561</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1922888604823806</v>
+        <v>0.007375514959965116</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.04</v>
       </c>
       <c r="C6" t="n">
-        <v>29.84185823490394</v>
+        <v>29.94241012696325</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1981417650960573</v>
+        <v>-0.09758987303674971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03926015907538115</v>
+        <v>0.009523783319328927</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.21</v>
       </c>
       <c r="C7" t="n">
-        <v>29.47979166439584</v>
+        <v>30.00820204159942</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7302083356041607</v>
+        <v>-0.2017979584005793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5332042133857985</v>
+        <v>0.04072241601464195</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.22</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87264849526314</v>
+        <v>30.14504543960305</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3473515047368636</v>
+        <v>-0.0749545603969537</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1206530678429634</v>
+        <v>0.005618186124300579</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.38</v>
       </c>
       <c r="C9" t="n">
-        <v>29.77935073574157</v>
+        <v>30.20597661290189</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6006492642584327</v>
+        <v>-0.1740233870981065</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3607795386541965</v>
+        <v>0.03028413925709742</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.44</v>
       </c>
       <c r="C10" t="n">
-        <v>30.44265920206595</v>
+        <v>30.49339099702649</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002659202065945721</v>
+        <v>0.05339099702649008</v>
       </c>
       <c r="E10" t="n">
-        <v>7.071355627529988e-06</v>
+        <v>0.002850598563482673</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.48</v>
       </c>
       <c r="C11" t="n">
-        <v>30.30459967519557</v>
+        <v>30.50756586496083</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.175400324804432</v>
+        <v>0.02756586496083102</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03076527394150025</v>
+        <v>0.0007598769110387715</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.69</v>
       </c>
       <c r="C12" t="n">
-        <v>30.50290512388348</v>
+        <v>30.51637331853345</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1870948761165252</v>
+        <v>-0.1736266814665548</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03500449266905791</v>
+        <v>0.03014622451708848</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.75</v>
       </c>
       <c r="C13" t="n">
-        <v>30.21830799828945</v>
+        <v>30.73448260021426</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5316920017105531</v>
+        <v>-0.01551739978573963</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2826963846829748</v>
+        <v>0.0002407896961104722</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.94</v>
       </c>
       <c r="C14" t="n">
-        <v>30.59245223777145</v>
+        <v>30.86336916496587</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3475477622285545</v>
+        <v>-0.07663083503413404</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1207894470300759</v>
+        <v>0.005872284878028665</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.95</v>
       </c>
       <c r="C15" t="n">
-        <v>30.80364098242264</v>
+        <v>31.03914848366619</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1463590175773639</v>
+        <v>0.08914848366618955</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02142096202621112</v>
+        <v>0.007947452139980864</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.02</v>
       </c>
       <c r="C16" t="n">
-        <v>31.36656043165091</v>
+        <v>31.21170990337458</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3465604316509072</v>
+        <v>0.1917099033745835</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1201041327860631</v>
+        <v>0.03675268705189214</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.12</v>
       </c>
       <c r="C17" t="n">
-        <v>31.68489189263112</v>
+        <v>31.27962889131896</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5648918926311168</v>
+        <v>0.1596288913189596</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3191028503603652</v>
+        <v>0.02548138294372023</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.28</v>
       </c>
       <c r="C18" t="n">
-        <v>31.75686389033347</v>
+        <v>31.11440397279001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4768638903334725</v>
+        <v>-0.1655960272099897</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2273991699039741</v>
+        <v>0.02742204422773164</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.38</v>
       </c>
       <c r="C19" t="n">
-        <v>31.45407467582688</v>
+        <v>30.89072679564211</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07407467582687843</v>
+        <v>-0.4892732043578896</v>
       </c>
       <c r="E19" t="n">
-        <v>0.005487057598857128</v>
+        <v>0.2393882685026372</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.58</v>
       </c>
       <c r="C20" t="n">
-        <v>31.8120608275237</v>
+        <v>31.11169872854706</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2320608275236999</v>
+        <v>-0.4683012714529333</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05385222767098441</v>
+        <v>0.219306080844434</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.65</v>
       </c>
       <c r="C21" t="n">
-        <v>31.76596772281332</v>
+        <v>31.65519723864403</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1159677228133233</v>
+        <v>0.005197238644029767</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0134485127345078</v>
+        <v>2.701128952299637e-05</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.88</v>
       </c>
       <c r="C22" t="n">
-        <v>32.43375460424933</v>
+        <v>32.54992960015406</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5537546042493311</v>
+        <v>0.6699296001540596</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3066441617273333</v>
+        <v>0.4488056691625781</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.28</v>
       </c>
       <c r="C23" t="n">
-        <v>32.27985246042758</v>
+        <v>32.57320848691319</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.000147539572417088</v>
+        <v>0.293208486913187</v>
       </c>
       <c r="E23" t="n">
-        <v>2.176792542901716e-08</v>
+        <v>0.08597121679792057</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.45</v>
       </c>
       <c r="C24" t="n">
-        <v>32.39661297351034</v>
+        <v>32.77063300299165</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.05338702648966631</v>
+        <v>0.3206330029916487</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002850174597408332</v>
+        <v>0.1028055226074426</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.85</v>
       </c>
       <c r="C25" t="n">
-        <v>32.67578202833903</v>
+        <v>32.97614095206262</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1742179716609726</v>
+        <v>0.1261409520626202</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03035190164966347</v>
+        <v>0.01591153978726425</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.9</v>
       </c>
       <c r="C26" t="n">
-        <v>32.81481145591957</v>
+        <v>33.03574193207213</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.08518854408042387</v>
+        <v>0.1357419320721291</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00725708804254232</v>
+        <v>0.01842587212267452</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.1</v>
       </c>
       <c r="C27" t="n">
-        <v>33.16627362188297</v>
+        <v>33.2519920345837</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0662736218829636</v>
+        <v>0.1519920345836994</v>
       </c>
       <c r="E27" t="n">
-        <v>0.004392192957486031</v>
+        <v>0.02310157857689247</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.4</v>
       </c>
       <c r="C28" t="n">
-        <v>33.80167156610683</v>
+        <v>33.5578811770355</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4016715661068275</v>
+        <v>0.157881177035506</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1613400470187115</v>
+        <v>0.02492646606211678</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.7</v>
       </c>
       <c r="C29" t="n">
-        <v>33.8928305017434</v>
+        <v>33.6559370622993</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1928305017434013</v>
+        <v>-0.04406293770070135</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03718360240261191</v>
+        <v>0.001941542478815889</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.1</v>
       </c>
       <c r="C30" t="n">
-        <v>33.97715446023061</v>
+        <v>33.75523765042924</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1228455397693935</v>
+        <v>-0.3447623495707646</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01509102664123364</v>
+        <v>0.1188610776815541</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.4</v>
       </c>
       <c r="C31" t="n">
-        <v>34.28860731142814</v>
+        <v>34.32940713013046</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1113926885718541</v>
+        <v>-0.07059286986953595</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01240833106726608</v>
+        <v>0.004983353276417236</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.9</v>
       </c>
       <c r="C32" t="n">
-        <v>34.58950825248252</v>
+        <v>34.63000944736938</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3104917475174815</v>
+        <v>-0.2699905526306168</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0964051252764595</v>
+        <v>0.07289489850978585</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.3</v>
       </c>
       <c r="C33" t="n">
-        <v>35.42654727823895</v>
+        <v>35.70998493816687</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1265472782389523</v>
+        <v>0.4099849381668719</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01601421362968681</v>
+        <v>0.1680876495236938</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.7</v>
       </c>
       <c r="C34" t="n">
-        <v>35.8361645363849</v>
+        <v>35.96754034663636</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1361645363848965</v>
+        <v>0.2675403466363591</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01854078096891379</v>
+        <v>0.07157783707830316</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.3</v>
       </c>
       <c r="C35" t="n">
-        <v>36.03483059126058</v>
+        <v>36.3516462931155</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2651694087394176</v>
+        <v>0.05164629311550328</v>
       </c>
       <c r="E35" t="n">
-        <v>0.07031481533121234</v>
+        <v>0.002667339592572482</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.8</v>
       </c>
       <c r="C36" t="n">
-        <v>36.94288902953851</v>
+        <v>36.87240230435085</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1428890295385159</v>
+        <v>0.07240230435085238</v>
       </c>
       <c r="E36" t="n">
-        <v>0.02041727476245887</v>
+        <v>0.005242093675313457</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.3</v>
       </c>
       <c r="C37" t="n">
-        <v>36.98994414241223</v>
+        <v>37.02096205104752</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3100558575877699</v>
+        <v>-0.2790379489524781</v>
       </c>
       <c r="E37" t="n">
-        <v>0.09613463482448743</v>
+        <v>0.07786217695560579</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.9</v>
       </c>
       <c r="C38" t="n">
-        <v>37.91515213975342</v>
+        <v>37.86916685439945</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01515213975342533</v>
+        <v>-0.03083314560055328</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0002295873391073323</v>
+        <v>0.0009506828676249181</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.5</v>
       </c>
       <c r="C39" t="n">
-        <v>38.53633178318749</v>
+        <v>38.57339737651738</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0363317831874852</v>
+        <v>0.07339737651738432</v>
       </c>
       <c r="E39" t="n">
-        <v>0.001319998469582432</v>
+        <v>0.005387174879634678</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.9</v>
       </c>
       <c r="C40" t="n">
-        <v>38.91602012685559</v>
+        <v>39.13221582775235</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01602012685558662</v>
+        <v>0.2322158277523556</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002566444644690878</v>
+        <v>0.05392419065871169</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.4</v>
       </c>
       <c r="C41" t="n">
-        <v>39.31561336749532</v>
+        <v>39.44683827096657</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.08438663250468181</v>
+        <v>0.04683827096657467</v>
       </c>
       <c r="E41" t="n">
-        <v>0.007121103745480221</v>
+        <v>0.002193823627138272</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.9</v>
       </c>
       <c r="C42" t="n">
-        <v>39.60958554336428</v>
+        <v>39.72154326227819</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2904144566357161</v>
+        <v>-0.1784567377218096</v>
       </c>
       <c r="E42" t="n">
-        <v>0.08434055662301822</v>
+        <v>0.03184680723831074</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.1</v>
       </c>
       <c r="C43" t="n">
-        <v>39.71877382572521</v>
+        <v>39.76597028438642</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3812261742747864</v>
+        <v>-0.3340297156135819</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1453333959521899</v>
+        <v>0.1115758509128904</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.6</v>
       </c>
       <c r="C44" t="n">
-        <v>39.85890062012768</v>
+        <v>39.89940613788547</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.7410993798723169</v>
+        <v>-0.7005938621145305</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5492282908471326</v>
+        <v>0.4908317596325537</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.9</v>
       </c>
       <c r="C45" t="n">
-        <v>40.13962008394929</v>
+        <v>40.18810999186909</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7603799160507094</v>
+        <v>-0.7118900081309079</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5781776167332839</v>
+        <v>0.506787383676624</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.2</v>
       </c>
       <c r="C46" t="n">
-        <v>41.00237829539187</v>
+        <v>41.19510746503966</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1976217046081317</v>
+        <v>-0.004892534960340811</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03905433813222365</v>
+        <v>2.393689833815706e-05</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.5</v>
       </c>
       <c r="C47" t="n">
-        <v>41.19383041310699</v>
+        <v>41.27281613400426</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.306169586893013</v>
+        <v>-0.227183865995741</v>
       </c>
       <c r="E47" t="n">
-        <v>0.09373981593823823</v>
+        <v>0.05161250896877081</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.8</v>
       </c>
       <c r="C48" t="n">
-        <v>41.77428316239367</v>
+        <v>41.706695964021</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.02571683760633192</v>
+        <v>-0.09330403597899561</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0006613557364704477</v>
+        <v>0.008705643129969708</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.2</v>
       </c>
       <c r="C49" t="n">
-        <v>42.15662985333856</v>
+        <v>42.37774458888481</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.04337014666144512</v>
+        <v>0.1777445888848064</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001880969621435259</v>
+        <v>0.03159313887782884</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.7</v>
       </c>
       <c r="C50" t="n">
-        <v>43.11398189751841</v>
+        <v>43.50534887802869</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4139818975184042</v>
+        <v>0.8053488780286884</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1713810114729385</v>
+        <v>0.6485868153420672</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>43.7</v>
       </c>
       <c r="C51" t="n">
-        <v>43.64995434627891</v>
+        <v>43.92497559223219</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.05004565372109226</v>
+        <v>0.224975592232191</v>
       </c>
       <c r="E51" t="n">
-        <v>0.002504567456371476</v>
+        <v>0.05061401710022508</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-2.763714210893195</v>
+        <v>0.1449619343228541</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>5.731464566825553</v>
+        <v>4.216651199693445</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1146292913365111</v>
+        <v>0.08433302399386891</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_8.xlsx
+++ b/partial/sliding_window_results_window_8.xlsx
@@ -463,13 +463,13 @@
         <v>29.84</v>
       </c>
       <c r="C2" t="n">
-        <v>30.26572128279039</v>
+        <v>29.97073419569709</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4257212827903949</v>
+        <v>0.1307341956970909</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1812386106206994</v>
+        <v>0.01709142992456526</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.81</v>
       </c>
       <c r="C3" t="n">
-        <v>30.13497992549404</v>
+        <v>29.84902875877324</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3249799254940449</v>
+        <v>0.03902875877323808</v>
       </c>
       <c r="E3" t="n">
-        <v>0.105611951974115</v>
+        <v>0.001523244011379609</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.92</v>
       </c>
       <c r="C4" t="n">
-        <v>29.88282032601017</v>
+        <v>29.83115154054451</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03717967398983291</v>
+        <v>-0.08884845945549102</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001382328157990258</v>
+        <v>0.007894048747614032</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.98</v>
       </c>
       <c r="C5" t="n">
-        <v>29.89411918165291</v>
+        <v>29.64783385498217</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08588081834708561</v>
+        <v>-0.3321661450178262</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007375514959965116</v>
+        <v>0.1103343478960035</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.04</v>
       </c>
       <c r="C6" t="n">
-        <v>29.94241012696325</v>
+        <v>29.89930664787337</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09758987303674971</v>
+        <v>-0.1406933521266254</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009523783319328927</v>
+        <v>0.0197946193326266</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.21</v>
       </c>
       <c r="C7" t="n">
-        <v>30.00820204159942</v>
+        <v>29.90498410820246</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2017979584005793</v>
+        <v>-0.3050158917975381</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04072241601464195</v>
+        <v>0.09303469424904745</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.22</v>
       </c>
       <c r="C8" t="n">
-        <v>30.14504543960305</v>
+        <v>30.12004944873262</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0749545603969537</v>
+        <v>-0.0999505512673764</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005618186124300579</v>
+        <v>0.009990112698652437</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.38</v>
       </c>
       <c r="C9" t="n">
-        <v>30.20597661290189</v>
+        <v>30.25802021166635</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1740233870981065</v>
+        <v>-0.1219797883336504</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03028413925709742</v>
+        <v>0.01487906876192216</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.44</v>
       </c>
       <c r="C10" t="n">
-        <v>30.49339099702649</v>
+        <v>30.63809028372575</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05339099702649008</v>
+        <v>0.198090283725751</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002850598563482673</v>
+        <v>0.03923976050654853</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.48</v>
       </c>
       <c r="C11" t="n">
-        <v>30.50756586496083</v>
+        <v>30.40690817453383</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02756586496083102</v>
+        <v>-0.07309182546617521</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0007598769110387715</v>
+        <v>0.005342414949977819</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.69</v>
       </c>
       <c r="C12" t="n">
-        <v>30.51637331853345</v>
+        <v>30.4279996484992</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1736266814665548</v>
+        <v>-0.2620003515007987</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03014622451708848</v>
+        <v>0.06864418418654207</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.75</v>
       </c>
       <c r="C13" t="n">
-        <v>30.73448260021426</v>
+        <v>30.63879034586218</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.01551739978573963</v>
+        <v>-0.1112096541378236</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0002407896961104722</v>
+        <v>0.01236758717345434</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.94</v>
       </c>
       <c r="C14" t="n">
-        <v>30.86336916496587</v>
+        <v>30.62093587076181</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.07663083503413404</v>
+        <v>-0.3190641292381891</v>
       </c>
       <c r="E14" t="n">
-        <v>0.005872284878028665</v>
+        <v>0.1018019185665238</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.95</v>
       </c>
       <c r="C15" t="n">
-        <v>31.03914848366619</v>
+        <v>30.69965318184731</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08914848366618955</v>
+        <v>-0.2503468181526891</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007947452139980864</v>
+        <v>0.06267352935917558</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.02</v>
       </c>
       <c r="C16" t="n">
-        <v>31.21170990337458</v>
+        <v>30.99620309597525</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1917099033745835</v>
+        <v>-0.02379690402474566</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03675268705189214</v>
+        <v>0.0005662926411629561</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.12</v>
       </c>
       <c r="C17" t="n">
-        <v>31.27962889131896</v>
+        <v>31.23592703345111</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1596288913189596</v>
+        <v>0.1159270334511042</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02548138294372023</v>
+        <v>0.01343907708477344</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.28</v>
       </c>
       <c r="C18" t="n">
-        <v>31.11440397279001</v>
+        <v>31.30887860752073</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1655960272099897</v>
+        <v>0.02887860752073124</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02742204422773164</v>
+        <v>0.0008339739723364347</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.38</v>
       </c>
       <c r="C19" t="n">
-        <v>30.89072679564211</v>
+        <v>31.23715241800889</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4892732043578896</v>
+        <v>-0.1428475819911093</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2393882685026372</v>
+        <v>0.02040543168070668</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.58</v>
       </c>
       <c r="C20" t="n">
-        <v>31.11169872854706</v>
+        <v>31.52227162109619</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4683012714529333</v>
+        <v>-0.05772837890381055</v>
       </c>
       <c r="E20" t="n">
-        <v>0.219306080844434</v>
+        <v>0.003332565730861919</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.65</v>
       </c>
       <c r="C21" t="n">
-        <v>31.65519723864403</v>
+        <v>31.55055311068767</v>
       </c>
       <c r="D21" t="n">
-        <v>0.005197238644029767</v>
+        <v>-0.09944688931233259</v>
       </c>
       <c r="E21" t="n">
-        <v>2.701128952299637e-05</v>
+        <v>0.00988968379389933</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.88</v>
       </c>
       <c r="C22" t="n">
-        <v>32.54992960015406</v>
+        <v>32.15356186491438</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6699296001540596</v>
+        <v>0.2735618649143809</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4488056691625781</v>
+        <v>0.07483609393543401</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.28</v>
       </c>
       <c r="C23" t="n">
-        <v>32.57320848691319</v>
+        <v>31.97473343331211</v>
       </c>
       <c r="D23" t="n">
-        <v>0.293208486913187</v>
+        <v>-0.3052665666878909</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08597121679792057</v>
+        <v>0.09318767673741253</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.45</v>
       </c>
       <c r="C24" t="n">
-        <v>32.77063300299165</v>
+        <v>32.21985751728705</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3206330029916487</v>
+        <v>-0.2301424827129566</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1028055226074426</v>
+        <v>0.05296556234928351</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.85</v>
       </c>
       <c r="C25" t="n">
-        <v>32.97614095206262</v>
+        <v>32.96751348420054</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1261409520626202</v>
+        <v>0.1175134842005434</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01591153978726425</v>
+        <v>0.01380941896895137</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.9</v>
       </c>
       <c r="C26" t="n">
-        <v>33.03574193207213</v>
+        <v>33.13401313537625</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1357419320721291</v>
+        <v>0.2340131353762516</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01842587212267452</v>
+        <v>0.05476214752862384</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.1</v>
       </c>
       <c r="C27" t="n">
-        <v>33.2519920345837</v>
+        <v>32.99735473281839</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1519920345836994</v>
+        <v>-0.1026452671816074</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02310157857689247</v>
+        <v>0.01053605087478356</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.4</v>
       </c>
       <c r="C28" t="n">
-        <v>33.5578811770355</v>
+        <v>33.58470787248725</v>
       </c>
       <c r="D28" t="n">
-        <v>0.157881177035506</v>
+        <v>0.1847078724872517</v>
       </c>
       <c r="E28" t="n">
-        <v>0.02492646606211678</v>
+        <v>0.03411699815876685</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.7</v>
       </c>
       <c r="C29" t="n">
-        <v>33.6559370622993</v>
+        <v>33.48171313924992</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.04406293770070135</v>
+        <v>-0.2182868607500836</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001941542478815889</v>
+        <v>0.0476491535761264</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.1</v>
       </c>
       <c r="C30" t="n">
-        <v>33.75523765042924</v>
+        <v>33.70241344639088</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3447623495707646</v>
+        <v>-0.3975865536091234</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1188610776815541</v>
+        <v>0.1580750676107804</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.4</v>
       </c>
       <c r="C31" t="n">
-        <v>34.32940713013046</v>
+        <v>34.14142127616188</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.07059286986953595</v>
+        <v>-0.2585787238381201</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004983353276417236</v>
+        <v>0.06686295642175077</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.9</v>
       </c>
       <c r="C32" t="n">
-        <v>34.63000944736938</v>
+        <v>34.73425485343664</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2699905526306168</v>
+        <v>-0.1657451465633599</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07289489850978585</v>
+        <v>0.02747145360930966</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.3</v>
       </c>
       <c r="C33" t="n">
-        <v>35.70998493816687</v>
+        <v>35.39671057406412</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4099849381668719</v>
+        <v>0.09671057406412586</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1680876495236938</v>
+        <v>0.009352935135812774</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.7</v>
       </c>
       <c r="C34" t="n">
-        <v>35.96754034663636</v>
+        <v>35.70552143734185</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2675403466363591</v>
+        <v>0.005521437341847957</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07157783707830316</v>
+        <v>3.048627031995303e-05</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.3</v>
       </c>
       <c r="C35" t="n">
-        <v>36.3516462931155</v>
+        <v>36.22442086159754</v>
       </c>
       <c r="D35" t="n">
-        <v>0.05164629311550328</v>
+        <v>-0.07557913840246044</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002667339592572482</v>
+        <v>0.005712206161658271</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.8</v>
       </c>
       <c r="C36" t="n">
-        <v>36.87240230435085</v>
+        <v>36.83505802009311</v>
       </c>
       <c r="D36" t="n">
-        <v>0.07240230435085238</v>
+        <v>0.03505802009311054</v>
       </c>
       <c r="E36" t="n">
-        <v>0.005242093675313457</v>
+        <v>0.001229064772848943</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.3</v>
       </c>
       <c r="C37" t="n">
-        <v>37.02096205104752</v>
+        <v>36.99488036620829</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2790379489524781</v>
+        <v>-0.3051196337917119</v>
       </c>
       <c r="E37" t="n">
-        <v>0.07786217695560579</v>
+        <v>0.09309799092518839</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.9</v>
       </c>
       <c r="C38" t="n">
-        <v>37.86916685439945</v>
+        <v>37.90146858575146</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.03083314560055328</v>
+        <v>0.001468585751460694</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0009506828676249181</v>
+        <v>2.15674410939337e-06</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.5</v>
       </c>
       <c r="C39" t="n">
-        <v>38.57339737651738</v>
+        <v>38.59820742885332</v>
       </c>
       <c r="D39" t="n">
-        <v>0.07339737651738432</v>
+        <v>0.09820742885332123</v>
       </c>
       <c r="E39" t="n">
-        <v>0.005387174879634678</v>
+        <v>0.009644699081980151</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.9</v>
       </c>
       <c r="C40" t="n">
-        <v>39.13221582775235</v>
+        <v>38.92648850701702</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2322158277523556</v>
+        <v>0.02648850701702088</v>
       </c>
       <c r="E40" t="n">
-        <v>0.05392419065871169</v>
+        <v>0.0007016410039907643</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.4</v>
       </c>
       <c r="C41" t="n">
-        <v>39.44683827096657</v>
+        <v>39.26934541470745</v>
       </c>
       <c r="D41" t="n">
-        <v>0.04683827096657467</v>
+        <v>-0.1306545852925467</v>
       </c>
       <c r="E41" t="n">
-        <v>0.002193823627138272</v>
+        <v>0.01707062065796736</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.9</v>
       </c>
       <c r="C42" t="n">
-        <v>39.72154326227819</v>
+        <v>39.72578984359784</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1784567377218096</v>
+        <v>-0.1742101564021539</v>
       </c>
       <c r="E42" t="n">
-        <v>0.03184680723831074</v>
+        <v>0.03034917859366291</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.1</v>
       </c>
       <c r="C43" t="n">
-        <v>39.76597028438642</v>
+        <v>39.60516913375433</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3340297156135819</v>
+        <v>-0.4948308662456711</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1115758509128904</v>
+        <v>0.2448575861894412</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.6</v>
       </c>
       <c r="C44" t="n">
-        <v>39.89940613788547</v>
+        <v>39.73369277813852</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.7005938621145305</v>
+        <v>-0.8663072218614829</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4908317596325537</v>
+        <v>0.7504882026493606</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.9</v>
       </c>
       <c r="C45" t="n">
-        <v>40.18810999186909</v>
+        <v>40.02188561152755</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7118900081309079</v>
+        <v>-0.8781143884724472</v>
       </c>
       <c r="E45" t="n">
-        <v>0.506787383676624</v>
+        <v>0.7710848792423398</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.2</v>
       </c>
       <c r="C46" t="n">
-        <v>41.19510746503966</v>
+        <v>41.30222617642076</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.004892534960340811</v>
+        <v>0.102226176420757</v>
       </c>
       <c r="E46" t="n">
-        <v>2.393689833815706e-05</v>
+        <v>0.01045019114560774</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.5</v>
       </c>
       <c r="C47" t="n">
-        <v>41.27281613400426</v>
+        <v>41.20070339314829</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.227183865995741</v>
+        <v>-0.299296606851712</v>
       </c>
       <c r="E47" t="n">
-        <v>0.05161250896877081</v>
+        <v>0.08957845887294826</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.8</v>
       </c>
       <c r="C48" t="n">
-        <v>41.706695964021</v>
+        <v>41.45489790812209</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.09330403597899561</v>
+        <v>-0.3451020918779051</v>
       </c>
       <c r="E48" t="n">
-        <v>0.008705643129969708</v>
+        <v>0.119095453818506</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.2</v>
       </c>
       <c r="C49" t="n">
-        <v>42.37774458888481</v>
+        <v>42.30349767206395</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1777445888848064</v>
+        <v>0.103497672063952</v>
       </c>
       <c r="E49" t="n">
-        <v>0.03159313887782884</v>
+        <v>0.01071176812265735</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.7</v>
       </c>
       <c r="C50" t="n">
-        <v>43.50534887802869</v>
+        <v>43.52450283659638</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8053488780286884</v>
+        <v>0.8245028365963734</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6485868153420672</v>
+        <v>0.679804927555466</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>43.7</v>
       </c>
       <c r="C51" t="n">
-        <v>43.92497559223219</v>
+        <v>43.73400761274357</v>
       </c>
       <c r="D51" t="n">
-        <v>0.224975592232191</v>
+        <v>0.03400761274356512</v>
       </c>
       <c r="E51" t="n">
-        <v>0.05061401710022508</v>
+        <v>0.001156517724516293</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.1449619343228541</v>
+        <v>-5.025508924175536</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>4.216651199693445</v>
+        <v>4.091769529707379</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.08433302399386891</v>
+        <v>0.08183539059414757</v>
       </c>
     </row>
   </sheetData>
